--- a/data/trans_camb/IP16A04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Clase-trans_camb.xlsx
@@ -636,12 +636,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,28</t>
+          <t>0,0; 17,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,25</t>
+          <t>0,0; 15,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 8,78</t>
+          <t>-13,85; 8,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 0,0</t>
+          <t>-24,2; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 3,21</t>
+          <t>-7,1; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 0,0</t>
+          <t>-12,41; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 1,05</t>
+          <t>-11,41; 1,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 3,6</t>
+          <t>-8,93; 4,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 0,93</t>
+          <t>-4,23; 1,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 2,04</t>
+          <t>-3,92; 2,56</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 0,0</t>
+          <t>-19,64; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 2,17</t>
+          <t>-17,24; 3,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 0,0</t>
+          <t>-9,83; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,42</t>
+          <t>-8,15; 2,38</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,68</t>
+          <t>0,0; 32,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,37</t>
+          <t>0,0; 37,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,59</t>
+          <t>2,38; 20,05</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,43</t>
+          <t>-3,89; 0,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,71</t>
+          <t>-1,72; 3,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,11</t>
+          <t>-2,9; 1,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,29</t>
+          <t>-3,39; 1,36</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,45</t>
+          <t>-2,59; 0,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,95</t>
+          <t>-1,44; 2,08</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-94,36; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-93,34; 144,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 283,93</t>
+          <t>-67,73; 347,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Clase-trans_camb.xlsx
@@ -636,12 +636,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,49</t>
+          <t>0,0; 18,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,12</t>
+          <t>0,0; 12,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 8,46</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 8,83</t>
+          <t>-13,92; 8,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 0,0</t>
+          <t>-22,09; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,18</t>
+          <t>-8,41; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 0,0</t>
+          <t>-10,92; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 1,05</t>
+          <t>-11,51; 1,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 4,02</t>
+          <t>-9,94; 3,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,36</t>
+          <t>-5,16; 1,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,56</t>
+          <t>-4,88; 2,33</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 0,0</t>
+          <t>-17,36; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 3,01</t>
+          <t>-14,51; 3,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 0,0</t>
+          <t>-10,45; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 2,38</t>
+          <t>-7,61; 2,74</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,82</t>
+          <t>0,0; 31,88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,52</t>
+          <t>0,0; 32,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,38; 20,05</t>
+          <t>2,43; 21,05</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,38</t>
+          <t>-4,13; 0,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,92</t>
+          <t>-1,53; 3,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,24</t>
+          <t>-3,21; 1,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,36</t>
+          <t>-3,33; 1,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,38</t>
+          <t>-2,59; 0,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,08</t>
+          <t>-1,46; 2,04</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,37; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,86; 120,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 347,8</t>
+          <t>-69,64; 341,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A04-Clase-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumieron medicamentos laxantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3,83</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,46</t>
+          <t>0,0; 8,9</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,55</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,8; 8,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,8; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 8,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 3,18</t>
+          <t>-7,3; 3,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 0,0</t>
+          <t>-10,77; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-5,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-1,36</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 1,07</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 3,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>-11,52; 1,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,57; 3,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,38</t>
+          <t>-5,37; 0,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,33</t>
+          <t>-4,27; 2,04</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-72,79%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-35,56%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-5,74</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,58</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,5</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-5,74</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,51; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>-16,45; 2,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 3,1</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 0,0</t>
+          <t>-11,32; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,74</t>
+          <t>-7,99; 2,42</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-62,4%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-62,4%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>5,94</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>10,56</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,88</t>
+          <t>0,0; 37,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,89</t>
+          <t>0,0; 31,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43; 21,05</t>
+          <t>0,0; 19,59</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,57</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,96</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,35</t>
+          <t>-3,11; 1,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,78</t>
+          <t>-3,37; 1,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,1</t>
+          <t>-3,67; 0,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,39</t>
+          <t>-1,97; 3,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,35</t>
+          <t>-2,57; 0,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,04</t>
+          <t>-1,66; 1,95</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-35,16%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-39,57%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-73,11%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>96,82%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-35,16%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-39,57%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-83,37; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-94,36; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-93,86; 120,08</t>
+          <t>-93,34; 144,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 341,98</t>
+          <t>-73,2; 283,93</t>
         </is>
       </c>
     </row>
